--- a/about/Leadership_2025-26.xlsx
+++ b/about/Leadership_2025-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/docs/apls-org/about/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B756D56C-D13B-8543-BC52-DE398435FD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEB448B-AFC7-8245-8129-75E85C29D577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="560" windowWidth="38680" windowHeight="13860" firstSheet="7" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2900" yWindow="560" windowWidth="16900" windowHeight="13320" firstSheet="19" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EC" sheetId="1" r:id="rId1"/>
@@ -2153,8 +2153,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2240,8 +2240,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2372,8 +2372,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2461,8 +2461,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2620,8 +2620,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2798,8 +2798,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2901,8 +2901,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3093,8 +3093,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3256,8 +3256,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3336,8 +3336,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3662,8 +3662,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3995,6 +3995,7 @@
     <row r="22" spans="1:10" ht="16" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="I17:J17"/>
@@ -4011,7 +4012,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{8E7A33AC-1B97-2A44-8663-826F3172ADED}"/>
@@ -4032,8 +4032,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4104,8 +4104,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4162,8 +4162,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4343,8 +4343,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4607,8 +4607,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4698,8 +4698,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -5024,8 +5024,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -5316,8 +5316,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>377</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>

--- a/about/Leadership_2025-26.xlsx
+++ b/about/Leadership_2025-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/docs/apls-org/about/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEB448B-AFC7-8245-8129-75E85C29D577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7C41D0-7D8B-DA48-A840-4A1B9F7F50F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="560" windowWidth="16900" windowHeight="13320" firstSheet="19" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14760" yWindow="660" windowWidth="14760" windowHeight="18980" firstSheet="20" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EC" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="494">
   <si>
     <t>Position</t>
   </si>
@@ -1502,12 +1502,6 @@
     <t xml:space="preserve">cassidyhaigh@ufl.edu </t>
   </si>
   <si>
-    <t>Member (past Chair)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle.Rynczak@umassmed.edu </t>
-  </si>
-  <si>
     <t xml:space="preserve">claduke@jjay.cuny.edu   </t>
   </si>
   <si>
@@ -1523,9 +1517,6 @@
     <t xml:space="preserve">2023–2026 </t>
   </si>
   <si>
-    <t>Minqi Pan</t>
-  </si>
-  <si>
     <t>Minqi.pan@gmail.com</t>
   </si>
   <si>
@@ -1535,9 +1526,6 @@
     <t>Jaymes Fairfax-Columbo</t>
   </si>
   <si>
-    <t>Marina Mukjin</t>
-  </si>
-  <si>
     <t>Kris@lefanlaw.com</t>
   </si>
   <si>
@@ -1545,6 +1533,24 @@
   </si>
   <si>
     <t>2024-2026</t>
+  </si>
+  <si>
+    <t>Member (Past Chair)</t>
+  </si>
+  <si>
+    <t>Karen Grabowski</t>
+  </si>
+  <si>
+    <t>Member (Subcommittee Chair of Embracing Leadership)</t>
+  </si>
+  <si>
+    <t>Minqi "Will" Pan</t>
+  </si>
+  <si>
+    <t>Member (Subcommittee Chair of Awards)</t>
+  </si>
+  <si>
+    <t>Marina Mukhin</t>
   </si>
 </sst>
 </file>
@@ -3995,23 +4001,23 @@
     <row r="22" spans="1:10" ht="16" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="I8:J8"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{8E7A33AC-1B97-2A44-8663-826F3172ADED}"/>
@@ -4336,7 +4342,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
@@ -4360,11 +4366,8 @@
       <c r="A2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
+      <c r="B2" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -4374,8 +4377,8 @@
       <c r="A3" t="s">
         <v>475</v>
       </c>
-      <c r="B3" t="s">
-        <v>191</v>
+      <c r="B3" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="C3" t="s">
         <v>476</v>
@@ -4385,42 +4388,39 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A4" t="s">
-        <v>477</v>
+      <c r="A4" s="2" t="s">
+        <v>488</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>478</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>44</v>
+      <c r="A5" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" t="s">
-        <v>479</v>
-      </c>
-      <c r="D5" t="s">
-        <v>128</v>
+        <v>489</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>227</v>
+      <c r="A6" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="C6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -4431,13 +4431,13 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>481</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
@@ -4445,13 +4445,13 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="D8" t="s">
-        <v>483</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
@@ -4459,13 +4459,13 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C9" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
@@ -4473,13 +4473,13 @@
         <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
@@ -4487,10 +4487,10 @@
         <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>486</v>
+        <v>324</v>
       </c>
       <c r="C11" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
         <v>232</v>
@@ -4501,10 +4501,10 @@
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D12" t="s">
         <v>232</v>
@@ -4515,13 +4515,13 @@
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>484</v>
       </c>
       <c r="C13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
@@ -4529,10 +4529,10 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D14" t="s">
         <v>51</v>
@@ -4543,13 +4543,13 @@
         <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>488</v>
+        <v>318</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D15" t="s">
-        <v>369</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
@@ -4557,10 +4557,10 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>493</v>
       </c>
       <c r="C16" t="s">
-        <v>489</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
         <v>369</v>
@@ -4571,25 +4571,41 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>490</v>
+        <v>322</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>485</v>
       </c>
       <c r="D17" t="s">
         <v>369</v>
       </c>
     </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>486</v>
+      </c>
+      <c r="C18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
+      <c r="C22" s="2"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="mailto:jamesrandretta@gmail.com" xr:uid="{EE5B9F96-C6E7-AC48-83AD-22F1843084FC}"/>
+    <hyperlink ref="C4" r:id="rId1" display="mailto:jamesrandretta@gmail.com" xr:uid="{EE5B9F96-C6E7-AC48-83AD-22F1843084FC}"/>
     <hyperlink ref="C3" r:id="rId2" display="mailto:cassidyhaigh@ufl.edu" xr:uid="{45A1E32E-96B9-CD4F-B5EA-E4D481235CFF}"/>
-    <hyperlink ref="C4" r:id="rId3" display="mailto:Danielle.Rynczak@umassmed.edu" xr:uid="{F24A39EB-D311-104B-864C-8DCD0165C543}"/>
-    <hyperlink ref="C5" r:id="rId4" display="mailto:claduke@jjay.cuny.edu" xr:uid="{F088E5FC-5CB6-6C4A-B09C-042C32CAB037}"/>
-    <hyperlink ref="C6" r:id="rId5" display="mailto:Lewis.douglas87@gmail.com" xr:uid="{AB412978-7E25-F946-8A7B-8C04F98BA354}"/>
-    <hyperlink ref="C8" r:id="rId6" display="mailto:afanniff@paloaltou.edu" xr:uid="{452527EB-61CC-9040-9B95-6AA119E9EF6F}"/>
-    <hyperlink ref="C13" r:id="rId7" display="mailto:erentzen@torontomu.ca" xr:uid="{1FBB85A3-AD73-4346-BA03-6A5FD4F8599A}"/>
-    <hyperlink ref="C14" r:id="rId8" display="mailto:daftarykaput@montclair.edu" xr:uid="{ADF073A2-4C7B-794E-8001-9DF0962FA8EE}"/>
+    <hyperlink ref="C7" r:id="rId3" display="mailto:claduke@jjay.cuny.edu" xr:uid="{F088E5FC-5CB6-6C4A-B09C-042C32CAB037}"/>
+    <hyperlink ref="C8" r:id="rId4" display="mailto:Lewis.douglas87@gmail.com" xr:uid="{AB412978-7E25-F946-8A7B-8C04F98BA354}"/>
+    <hyperlink ref="C10" r:id="rId5" display="mailto:afanniff@paloaltou.edu" xr:uid="{452527EB-61CC-9040-9B95-6AA119E9EF6F}"/>
+    <hyperlink ref="C14" r:id="rId6" display="mailto:erentzen@torontomu.ca" xr:uid="{1FBB85A3-AD73-4346-BA03-6A5FD4F8599A}"/>
+    <hyperlink ref="C15" r:id="rId7" display="mailto:daftarykaput@montclair.edu" xr:uid="{ADF073A2-4C7B-794E-8001-9DF0962FA8EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4631,7 +4647,7 @@
         <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
